--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>87</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$102</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3305" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3703" uniqueCount="485">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -882,6 +882,142 @@
     <t>RXO-5-Requested Dosage Form / RXE-6-Give Dosage Form / RXD-6-Actual Dosage Form / RXG-8-Give Dosage Form / RXA-8-Administered Dosage Form</t>
   </si>
   <si>
+    <t>Medication.form.id</t>
+  </si>
+  <si>
+    <t>Medication.form.extension</t>
+  </si>
+  <si>
+    <t>Medication.form.coding</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.id</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.extension</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Medication.form.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
     <t>Medication.amount</t>
   </si>
   <si>
@@ -1146,10 +1282,6 @@
     <t>Medication.ingredient.isActive</t>
   </si>
   <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
     <t>Active ingredient indicator</t>
   </si>
   <si>
@@ -1251,127 +1383,31 @@
     <t>Medication.ingredient.item[x].coding.system</t>
   </si>
   <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
     <t>https://termgit.elga.gv.at/CodeSystem/atc-deutsch-wido</t>
   </si>
   <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
     <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.version</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding.version</t>
   </si>
   <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
     <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.code</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding.code</t>
   </si>
   <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
     <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.display</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding.display</t>
   </si>
   <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
     <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.userSelected</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
   </si>
   <si>
     <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges</t>
@@ -1810,7 +1846,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN91"/>
+  <dimension ref="A1:AN102"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="66.546875" customWidth="true" bestFit="true"/>
@@ -5492,7 +5528,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>275</v>
       </c>
@@ -5511,22 +5547,22 @@
         <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>276</v>
+        <v>101</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>277</v>
+        <v>102</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>278</v>
+        <v>103</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5577,7 +5613,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>275</v>
+        <v>104</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5589,13 +5625,13 @@
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>279</v>
+        <v>105</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
@@ -5606,21 +5642,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
@@ -5632,15 +5668,17 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5677,31 +5715,31 @@
         <v>21</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>21</v>
@@ -5716,46 +5754,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>109</v>
+        <v>237</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>110</v>
+        <v>238</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5791,19 +5831,19 @@
         <v>21</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>115</v>
+        <v>241</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5815,27 +5855,27 @@
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>105</v>
+        <v>242</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>21</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5843,28 +5883,28 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>283</v>
+        <v>101</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>284</v>
+        <v>102</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>285</v>
+        <v>103</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5915,7 +5955,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>286</v>
+        <v>104</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5927,13 +5967,13 @@
         <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>287</v>
+        <v>105</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
@@ -5944,21 +5984,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>21</v>
@@ -5970,15 +6010,17 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6015,31 +6057,31 @@
         <v>21</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>21</v>
@@ -6054,46 +6096,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>109</v>
+        <v>281</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>110</v>
+        <v>282</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6129,51 +6173,51 @@
         <v>21</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>115</v>
+        <v>285</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>105</v>
+        <v>286</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>21</v>
+        <v>287</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6181,7 +6225,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>87</v>
@@ -6196,20 +6240,18 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L39" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>295</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6257,7 +6299,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6275,21 +6317,21 @@
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6297,16 +6339,16 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>88</v>
@@ -6315,21 +6357,19 @@
         <v>163</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q40" t="s" s="2">
-        <v>303</v>
-      </c>
+      <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6349,13 +6389,13 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>304</v>
+        <v>21</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>305</v>
+        <v>21</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -6373,7 +6413,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6391,21 +6431,21 @@
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6431,14 +6471,14 @@
         <v>101</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6487,7 +6527,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6505,21 +6545,21 @@
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6542,17 +6582,19 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>129</v>
+        <v>310</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O42" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6601,7 +6643,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6610,7 +6652,7 @@
         <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>321</v>
+        <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>99</v>
@@ -6619,21 +6661,21 @@
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6641,13 +6683,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6656,19 +6698,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>325</v>
+        <v>246</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>326</v>
+        <v>247</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>327</v>
+        <v>248</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6693,11 +6735,13 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -6715,7 +6759,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>329</v>
+        <v>249</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6733,21 +6777,21 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>330</v>
+        <v>250</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>315</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6755,7 +6799,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>87</v>
@@ -6770,13 +6814,13 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6827,7 +6871,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6845,7 +6889,7 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
@@ -6856,10 +6900,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6968,10 +7012,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7082,10 +7126,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7108,20 +7152,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>291</v>
+        <v>328</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7169,7 +7209,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7187,21 +7227,21 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>297</v>
+        <v>332</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>298</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7212,36 +7252,32 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>300</v>
+        <v>102</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>301</v>
+        <v>103</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>302</v>
-      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q48" t="s" s="2">
-        <v>303</v>
-      </c>
+      <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7261,13 +7297,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>304</v>
+        <v>21</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>305</v>
+        <v>21</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7285,7 +7321,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>306</v>
+        <v>104</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7297,61 +7333,61 @@
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>307</v>
+        <v>105</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>308</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>310</v>
+        <v>109</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7387,51 +7423,51 @@
         <v>21</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>313</v>
+        <v>115</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>314</v>
+        <v>105</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>315</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7439,13 +7475,13 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -7454,17 +7490,19 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>129</v>
+        <v>336</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7513,7 +7551,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7522,7 +7560,7 @@
         <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>321</v>
+        <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>99</v>
@@ -7531,21 +7569,21 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>315</v>
+        <v>343</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7556,13 +7594,13 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I51" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>88</v>
@@ -7571,21 +7609,21 @@
         <v>163</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q51" s="2"/>
+      <c r="Q51" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="R51" t="s" s="2">
         <v>21</v>
       </c>
@@ -7607,9 +7645,11 @@
       <c r="X51" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Y51" s="2"/>
+      <c r="Y51" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -7627,7 +7667,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7645,21 +7685,21 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>315</v>
+        <v>353</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7667,10 +7707,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>88</v>
@@ -7679,21 +7719,21 @@
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>344</v>
+        <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -7729,23 +7769,25 @@
         <v>21</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AC52" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
@@ -7757,21 +7799,21 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7791,19 +7833,21 @@
         <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>102</v>
+        <v>362</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>103</v>
+        <v>363</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -7851,7 +7895,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>104</v>
+        <v>365</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7860,64 +7904,66 @@
         <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>21</v>
+        <v>366</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>105</v>
+        <v>367</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>109</v>
+        <v>369</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>110</v>
+        <v>370</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -7941,13 +7987,11 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>21</v>
+        <v>373</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -7965,39 +8009,39 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>115</v>
+        <v>374</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>105</v>
+        <v>375</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8005,28 +8049,28 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>108</v>
+        <v>328</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>214</v>
+        <v>377</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>205</v>
+        <v>378</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8077,25 +8121,25 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>21</v>
+        <v>380</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -8104,12 +8148,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8117,13 +8161,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
@@ -8132,18 +8176,16 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>224</v>
+        <v>101</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>355</v>
+        <v>102</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>356</v>
+        <v>103</v>
       </c>
       <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>357</v>
-      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8191,10 +8233,10 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>354</v>
+        <v>104</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>87</v>
@@ -8203,38 +8245,38 @@
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>358</v>
+        <v>105</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>359</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -8246,18 +8288,18 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>361</v>
+        <v>108</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>362</v>
+        <v>109</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8293,37 +8335,37 @@
         <v>21</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>360</v>
+        <v>115</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>365</v>
+        <v>105</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
@@ -8332,12 +8374,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8345,31 +8387,35 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>276</v>
+        <v>336</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8417,7 +8463,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8432,64 +8478,64 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>279</v>
+        <v>342</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>370</v>
+        <v>343</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I59" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I59" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>344</v>
+        <v>163</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="M59" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q59" s="2"/>
+      <c r="Q59" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="R59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8509,13 +8555,13 @@
         <v>21</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>21</v>
+        <v>349</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>21</v>
+        <v>350</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>21</v>
@@ -8533,13 +8579,13 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
@@ -8551,21 +8597,21 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8579,25 +8625,27 @@
         <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>102</v>
+        <v>355</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>103</v>
+        <v>356</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8645,7 +8693,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>104</v>
+        <v>358</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8657,38 +8705,38 @@
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>105</v>
+        <v>359</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>351</v>
+        <v>386</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -8697,21 +8745,21 @@
         <v>21</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>109</v>
+        <v>362</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -8759,39 +8807,39 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>115</v>
+        <v>365</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>21</v>
+        <v>366</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>105</v>
+        <v>367</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>352</v>
+        <v>387</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8802,28 +8850,32 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -8847,13 +8899,11 @@
         <v>21</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>21</v>
+        <v>373</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -8871,39 +8921,39 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>21</v>
+        <v>375</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>354</v>
+        <v>388</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8914,7 +8964,7 @@
         <v>87</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>88</v>
@@ -8926,18 +8976,18 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>224</v>
+        <v>389</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -8973,25 +9023,23 @@
         <v>21</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>354</v>
+        <v>388</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
@@ -9000,24 +9048,24 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>358</v>
+        <v>394</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>359</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9126,10 +9174,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9199,16 +9247,16 @@
         <v>21</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>115</v>
@@ -9240,10 +9288,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9251,35 +9299,31 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I66" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9315,17 +9359,19 @@
         <v>21</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AC66" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>241</v>
+        <v>398</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9337,37 +9383,35 @@
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>87</v>
@@ -9379,22 +9423,20 @@
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>141</v>
+        <v>224</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>237</v>
+        <v>400</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>240</v>
+        <v>402</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9443,13 +9485,13 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>241</v>
+        <v>399</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
@@ -9458,24 +9500,24 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>21</v>
+        <v>230</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>242</v>
+        <v>403</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>243</v>
+        <v>404</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9498,16 +9540,18 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>101</v>
+        <v>310</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>102</v>
+        <v>406</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>103</v>
+        <v>407</v>
       </c>
       <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
       </c>
@@ -9555,7 +9599,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>104</v>
+        <v>405</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9567,13 +9611,13 @@
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>105</v>
+        <v>409</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>21</v>
@@ -9584,21 +9628,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -9610,17 +9654,15 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>108</v>
+        <v>321</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>109</v>
+        <v>411</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -9657,53 +9699,55 @@
         <v>21</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>115</v>
+        <v>410</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>21</v>
+        <v>413</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>105</v>
+        <v>324</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>21</v>
+        <v>414</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="D70" t="s" s="2">
         <v>21</v>
       </c>
@@ -9712,7 +9756,7 @@
         <v>87</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>88</v>
@@ -9721,23 +9765,21 @@
         <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>129</v>
+        <v>389</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
@@ -9746,7 +9788,7 @@
         <v>21</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>399</v>
+        <v>21</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>21</v>
@@ -9785,13 +9827,13 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
@@ -9803,21 +9845,21 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>402</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9831,26 +9873,24 @@
         <v>87</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>405</v>
+        <v>102</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -9899,7 +9939,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>408</v>
+        <v>104</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9911,61 +9951,61 @@
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>409</v>
+        <v>105</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>410</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>413</v>
+        <v>109</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
@@ -10013,39 +10053,39 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>416</v>
+        <v>115</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>417</v>
+        <v>105</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>418</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>420</v>
+        <v>397</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10056,30 +10096,28 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I73" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>421</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>422</v>
+        <v>205</v>
       </c>
       <c r="N73" s="2"/>
-      <c r="O73" t="s" s="2">
-        <v>423</v>
-      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>21</v>
       </c>
@@ -10127,39 +10165,39 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>424</v>
+        <v>398</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>425</v>
+        <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>426</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>428</v>
+        <v>399</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10167,34 +10205,32 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>361</v>
+        <v>224</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10243,10 +10279,10 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>433</v>
+        <v>399</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>87</v>
@@ -10258,28 +10294,26 @@
         <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>21</v>
+        <v>230</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>434</v>
+        <v>403</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>435</v>
+        <v>404</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>21</v>
       </c>
@@ -10291,29 +10325,25 @@
         <v>87</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>237</v>
+        <v>102</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
       </c>
@@ -10361,50 +10391,50 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>241</v>
+        <v>104</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>242</v>
+        <v>105</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>390</v>
+        <v>427</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
@@ -10416,15 +10446,17 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -10461,31 +10493,31 @@
         <v>21</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>21</v>
@@ -10502,44 +10534,46 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>392</v>
+        <v>429</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>109</v>
+        <v>237</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>110</v>
+        <v>238</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -10575,11 +10609,9 @@
         <v>21</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="AC77" s="2"/>
       <c r="AD77" t="s" s="2">
         <v>21</v>
       </c>
@@ -10587,7 +10619,7 @@
         <v>114</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>115</v>
+        <v>241</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10599,35 +10631,37 @@
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>105</v>
+        <v>242</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>21</v>
+        <v>243</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>87</v>
@@ -10642,19 +10676,19 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>395</v>
+        <v>237</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>396</v>
+        <v>238</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>397</v>
+        <v>239</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>398</v>
+        <v>240</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -10664,7 +10698,7 @@
         <v>21</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>441</v>
+        <v>21</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>21</v>
@@ -10703,13 +10737,13 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>400</v>
+        <v>241</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>21</v>
@@ -10721,21 +10755,21 @@
         <v>21</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>401</v>
+        <v>242</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>402</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10749,26 +10783,24 @@
         <v>87</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>405</v>
+        <v>102</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -10817,7 +10849,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>408</v>
+        <v>104</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10829,61 +10861,61 @@
         <v>21</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>409</v>
+        <v>105</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>410</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>413</v>
+        <v>109</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>21</v>
       </c>
@@ -10919,51 +10951,51 @@
         <v>21</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>416</v>
+        <v>115</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>417</v>
+        <v>105</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>418</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10971,7 +11003,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>87</v>
@@ -10986,17 +11018,19 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>421</v>
+        <v>281</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O81" t="s" s="2">
-        <v>423</v>
+        <v>284</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -11006,7 +11040,7 @@
         <v>21</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>21</v>
@@ -11045,7 +11079,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>424</v>
+        <v>285</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11063,21 +11097,21 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>425</v>
+        <v>286</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>426</v>
+        <v>287</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11091,7 +11125,7 @@
         <v>87</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>21</v>
@@ -11100,20 +11134,18 @@
         <v>88</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>361</v>
+        <v>101</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>429</v>
+        <v>289</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>430</v>
+        <v>290</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>21</v>
       </c>
@@ -11161,7 +11193,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>433</v>
+        <v>292</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11179,21 +11211,21 @@
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>434</v>
+        <v>293</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>435</v>
+        <v>294</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11201,13 +11233,13 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>21</v>
@@ -11216,19 +11248,17 @@
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -11277,7 +11307,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>249</v>
+        <v>299</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11295,21 +11325,21 @@
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>251</v>
+        <v>301</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>360</v>
+        <v>445</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11317,7 +11347,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>87</v>
@@ -11329,20 +11359,20 @@
         <v>21</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>361</v>
+        <v>101</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>362</v>
+        <v>303</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>363</v>
+        <v>304</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>364</v>
+        <v>305</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -11352,7 +11382,7 @@
         <v>21</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>21</v>
@@ -11391,7 +11421,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>360</v>
+        <v>306</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11409,21 +11439,21 @@
         <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>365</v>
+        <v>307</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>21</v>
+        <v>308</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>366</v>
+        <v>447</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11437,25 +11467,29 @@
         <v>87</v>
       </c>
       <c r="H85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J85" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K85" t="s" s="2">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>451</v>
+        <v>311</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
       </c>
@@ -11503,7 +11537,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>366</v>
+        <v>315</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11518,26 +11552,28 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>279</v>
+        <v>316</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>370</v>
+        <v>317</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="D86" t="s" s="2">
         <v>21</v>
       </c>
@@ -11549,25 +11585,29 @@
         <v>87</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>344</v>
+        <v>141</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>453</v>
+        <v>237</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
       </c>
@@ -11615,13 +11655,13 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>452</v>
+        <v>241</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>21</v>
@@ -11630,24 +11670,24 @@
         <v>99</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>455</v>
+        <v>242</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>21</v>
+        <v>243</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>456</v>
+        <v>434</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11756,10 +11796,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11829,16 +11869,16 @@
         <v>21</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>115</v>
@@ -11868,47 +11908,47 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>459</v>
+        <v>21</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J89" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>460</v>
+        <v>281</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>461</v>
+        <v>282</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>462</v>
+        <v>284</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>21</v>
@@ -11918,7 +11958,7 @@
         <v>21</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>21</v>
+        <v>453</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>21</v>
@@ -11957,39 +11997,39 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>353</v>
+        <v>285</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>188</v>
+        <v>286</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>21</v>
+        <v>287</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12003,24 +12043,26 @@
         <v>87</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K90" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>464</v>
+        <v>289</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -12069,7 +12111,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>463</v>
+        <v>292</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12084,24 +12126,24 @@
         <v>99</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>221</v>
+        <v>293</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>466</v>
+        <v>294</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12109,31 +12151,33 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>468</v>
+        <v>163</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>469</v>
+        <v>296</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>470</v>
+        <v>297</v>
       </c>
       <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>21</v>
       </c>
@@ -12181,7 +12225,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>467</v>
+        <v>299</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12196,20 +12240,1270 @@
         <v>99</v>
       </c>
       <c r="AK91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK97" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AL91" t="s" s="2">
+      <c r="AL97" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AM91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN91" t="s" s="2">
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>472</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>484</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN91">
+  <autoFilter ref="A1:AN102">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12219,7 +13513,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI90">
+  <conditionalFormatting sqref="A2:AI101">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1096,7 +1096,7 @@
     <t>Medication.amount.numerator.comparator</t>
   </si>
   <si>
-    <t>Fachliche Begründung: TODO</t>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
   </si>
   <si>
     <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
@@ -12513,7 +12513,7 @@
         <v>101</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>345</v>
+        <v>319</v>
       </c>
       <c r="M94" t="s" s="2">
         <v>246</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-wirkstoff.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
